--- a/docs/ValueSet-serviceConnected.xlsx
+++ b/docs/ValueSet-serviceConnected.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
